--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484779_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484779_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.453</v>
+        <v>2.5525</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6895</v>
+        <v>0.7096</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7635</v>
+        <v>1.8428</v>
       </c>
       <c r="G2" t="n">
         <v>1.2724</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>0.124</v>
+        <v>0.2235</v>
       </c>
       <c r="T2" t="n">
-        <v>0.074</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05</v>
+        <v>0.1294</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0641</v>
+        <v>2.1973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5042</v>
+        <v>0.8754</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5599</v>
+        <v>1.3218</v>
       </c>
       <c r="G3" t="n">
         <v>2.3221</v>
@@ -688,13 +688,13 @@
         <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2204</v>
+        <v>-0.0873</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7519</v>
+        <v>-0.3807</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5315</v>
+        <v>0.2934</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6036</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.524</v>
+        <v>1.2837</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4756</v>
+        <v>-0.6101</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9996</v>
+        <v>1.8938</v>
       </c>
       <c r="G4" t="n">
         <v>1.2048</v>
@@ -766,13 +766,13 @@
         <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5079</v>
+        <v>0.2676</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1582</v>
+        <v>-0.2927</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6661</v>
+        <v>0.5603</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3254</v>
+        <v>1.2509</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4788</v>
+        <v>1.2509</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8041</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6515</v>
+        <v>1.2509</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1341</v>
+        <v>0.6339</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4827</v>
+        <v>0.617</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0337</v>
+        <v>1.2509</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.7585</v>
+        <v>0.6339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7248</v>
+        <v>0.617</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3823</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3756</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4673</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2533</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2509</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2509</v>
+        <v>-1.0231</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.8835</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2509</v>
+        <v>-0.6515</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6339</v>
+        <v>-2.1341</v>
       </c>
       <c r="I6" t="n">
-        <v>0.617</v>
+        <v>1.4827</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2509</v>
+        <v>-1.0337</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6339</v>
+        <v>-1.7585</v>
       </c>
       <c r="L6" t="n">
-        <v>0.617</v>
+        <v>0.7248</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.3823</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.3756</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.7579</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.291</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2934</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6594</v>
+        <v>-0.2172</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1638</v>
+        <v>-2.6952</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5044</v>
+        <v>2.478</v>
       </c>
       <c r="G8" t="n">
         <v>0.0101</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.726</v>
+        <v>-0.2838</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1046</v>
+        <v>-0.636</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3786</v>
+        <v>0.3522</v>
       </c>
       <c r="V8" t="n">
         <v>0.6226</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3695</v>
+        <v>-1.2192</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5719</v>
+        <v>-1.4745</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2024</v>
+        <v>0.2553</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1696</v>
@@ -1156,13 +1156,13 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3886</v>
+        <v>-0.2382</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2939</v>
+        <v>-0.1965</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3614</v>
+        <v>-1.6593</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8462</v>
+        <v>-0.7157</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4847</v>
+        <v>-0.9436</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4415</v>
+        <v>1.4321</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3983</v>
+        <v>0.9947</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0431</v>
+        <v>0.4374</v>
       </c>
       <c r="J10" t="n">
-        <v>0.263</v>
+        <v>1.1684</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5596</v>
+        <v>1.0776</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8226</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7045</v>
+        <v>0.2637</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1612</v>
+        <v>-0.0829</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8657</v>
+        <v>0.3466</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4531</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1557</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.0029</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4909</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6226</v>
+        <v>-2.7922</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6226</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4282</v>
+        <v>-3.1459</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4582</v>
+        <v>-3.3132</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9701</v>
+        <v>0.1673</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4321</v>
+        <v>-0.4415</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9947</v>
+        <v>-0.3983</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4374</v>
+        <v>-0.0431</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1684</v>
+        <v>0.263</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0776</v>
+        <v>-0.5596</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.8226</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2637</v>
+        <v>-0.7045</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0829</v>
+        <v>0.1612</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3466</v>
+        <v>-0.8657</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3774</v>
+        <v>-2.4531</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6907</v>
+        <v>0.3712</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7396</v>
+        <v>0.1978</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0489</v>
+        <v>0.1735</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7922</v>
+        <v>-0.6226</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7922</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4773</v>
+        <v>-4.4194</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5835</v>
+        <v>-0.7637</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8938</v>
+        <v>-3.6557</v>
       </c>
       <c r="G12" t="n">
         <v>0.5068</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6448</v>
+        <v>-0.587</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8107</v>
+        <v>0.0091</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8341</v>
+        <v>-0.596</v>
       </c>
       <c r="V12" t="n">
         <v>-4.3392</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.3786</v>
+        <v>-9.4833</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.3283</v>
+        <v>-7.6446</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0504</v>
+        <v>-1.8387</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9634</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.415</v>
+        <v>-0.5196</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.281</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.134</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8488</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.4231</v>
+        <v>-11.3656</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.8278</v>
+        <v>-14.7703</v>
       </c>
       <c r="F14" t="n">
-        <v>3.404299999999999</v>
+        <v>3.404500000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4071</v>
+        <v>3.407100000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8138000000000002</v>
+        <v>-0.8137999999999997</v>
       </c>
       <c r="I14" t="n">
         <v>4.2209</v>
@@ -1525,10 +1525,10 @@
         <v>0.2579999999999995</v>
       </c>
       <c r="L14" t="n">
-        <v>3.460900000000001</v>
+        <v>3.4609</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3118000000000004</v>
+        <v>-0.3118000000000002</v>
       </c>
       <c r="N14" t="n">
         <v>-1.0719</v>
@@ -1546,13 +1546,13 @@
         <v>14.1525</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8306</v>
+        <v>-0.773</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.147799999999999</v>
+        <v>-2.0902</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3173</v>
+        <v>1.3175</v>
       </c>
       <c r="V14" t="n">
         <v>-7.395199999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3244</v>
+        <v>6.586</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9825</v>
+        <v>3.5927</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3419</v>
+        <v>2.9932</v>
       </c>
       <c r="G15" t="n">
         <v>0.9483</v>
@@ -1624,13 +1624,13 @@
         <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>1.395</v>
+        <v>0.6566</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1582</v>
+        <v>-0.548</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5532</v>
+        <v>1.2046</v>
       </c>
       <c r="V15" t="n">
         <v>3.094</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2099</v>
+        <v>3.0818</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6137</v>
+        <v>1.8343</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5962</v>
+        <v>1.2475</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9792</v>
@@ -1702,13 +1702,13 @@
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0569</v>
+        <v>0.9288</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3608</v>
+        <v>0.5813</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.3475</v>
       </c>
       <c r="V16" t="n">
         <v>1.2452</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5932</v>
+        <v>1.9407</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2464</v>
+        <v>-0.3438</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8395</v>
+        <v>2.2845</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6446</v>
@@ -1780,13 +1780,13 @@
         <v>3.3966</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2193</v>
+        <v>0.5668</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1582</v>
+        <v>-0.2557</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3775</v>
+        <v>0.8225</v>
       </c>
       <c r="V17" t="n">
         <v>1.8298</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2642</v>
+        <v>1.7477</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5541</v>
+        <v>0.749</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7101</v>
+        <v>0.9987</v>
       </c>
       <c r="G18" t="n">
         <v>1.5549</v>
@@ -1858,13 +1858,13 @@
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2945</v>
+        <v>0.778</v>
       </c>
       <c r="T18" t="n">
-        <v>0.238</v>
+        <v>0.4329</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0565</v>
+        <v>0.3451</v>
       </c>
       <c r="V18" t="n">
         <v>0.9244</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2715</v>
+        <v>0.5956</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.013</v>
+        <v>-1.9873</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2845</v>
+        <v>2.5829</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8965</v>
+        <v>0.5569</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5912</v>
+        <v>1.2169</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6947</v>
+        <v>-0.6601</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6616</v>
+        <v>1.6516</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3126</v>
+        <v>1.5112</v>
       </c>
       <c r="L21" t="n">
-        <v>0.651</v>
+        <v>0.1404</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2349</v>
+        <v>-1.0947</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2786</v>
+        <v>-0.2942</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0437</v>
+        <v>-0.8005</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2644</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3209</v>
+        <v>-3.9627</v>
       </c>
       <c r="R21" t="n">
-        <v>3.5853</v>
+        <v>3.0192</v>
       </c>
       <c r="S21" t="n">
-        <v>0.847</v>
+        <v>0.3596</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6677</v>
+        <v>-0.2988</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1793</v>
+        <v>0.6585</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9434</v>
+        <v>0.6226</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2303</v>
+        <v>0.2666</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.214</v>
+        <v>-2.5976</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4444</v>
+        <v>2.8642</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0818</v>
+        <v>-1.8965</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0697</v>
+        <v>-2.5912</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1515</v>
+        <v>0.6947</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0211</v>
+        <v>-1.6616</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0211</v>
+        <v>-2.3126</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.651</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.103</v>
+        <v>-0.2349</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0485</v>
+        <v>-0.2786</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1515</v>
+        <v>0.0437</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3774</v>
+        <v>2.2644</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3774</v>
+        <v>3.5853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.8421</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2352</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1699</v>
+        <v>0.759</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4906</v>
+        <v>0.2484</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8642</v>
+        <v>-0.1166</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3736</v>
+        <v>0.365</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5569</v>
+        <v>-0.0818</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2169</v>
+        <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6601</v>
+        <v>-0.1515</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6516</v>
+        <v>0.0211</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5112</v>
+        <v>0.0211</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1404</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0947</v>
+        <v>-0.103</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2942</v>
+        <v>0.0485</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8005</v>
+        <v>-0.1515</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9627</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.0192</v>
+        <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7266</v>
+        <v>-0.0472</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1758</v>
+        <v>-0.1377</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4492</v>
+        <v>0.0905</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. FUERTES DOMENECH</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5344</v>
+        <v>-0.1517</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2851</v>
+        <v>-1.8725</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2493</v>
+        <v>1.7208</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1182</v>
+        <v>-1.4138</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1182</v>
+        <v>-0.0023</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-1.4115</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0211</v>
+        <v>-1.3804</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0211</v>
+        <v>-0.1636</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-1.2169</v>
       </c>
       <c r="M24" t="n">
-        <v>0.097</v>
+        <v>-0.0334</v>
       </c>
       <c r="N24" t="n">
-        <v>0.097</v>
+        <v>0.1612</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>-0.1946</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.1887</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1587</v>
+        <v>0.3186</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1176</v>
+        <v>-0.3034</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2763</v>
+        <v>0.622</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. CAMBRA NADAL</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7309</v>
+        <v>-0.1856</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7083</v>
+        <v>-3.5538</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0226</v>
+        <v>3.3682</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7309</v>
+        <v>-2.723</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8609</v>
+        <v>0.6136</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1299</v>
+        <v>-3.3366</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6496</v>
+        <v>-3.1608</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6496</v>
+        <v>0.1111</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-3.2719</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0814</v>
+        <v>0.4378</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2113</v>
+        <v>0.5024</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1299</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.6418</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-0.4061</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0588</v>
+        <v>-0.6947</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0588</v>
+        <v>0.2887</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>P. FUERTES DOMENECH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7531</v>
+        <v>-0.5609</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.2622</v>
+        <v>-0.2851</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5092</v>
+        <v>-0.2757</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.4138</v>
+        <v>0.1182</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0023</v>
+        <v>0.1182</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.4115</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3804</v>
+        <v>0.0211</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1636</v>
+        <v>0.0211</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2169</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0334</v>
+        <v>0.097</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1612</v>
+        <v>0.097</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1946</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q26" t="n">
         <v>-0.1887</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2828</v>
+        <v>0.1323</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6931</v>
+        <v>-0.1176</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4104</v>
+        <v>0.2498</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>V. CAMBRA NADAL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,64 +2515,64 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8459</v>
+        <v>-0.7309</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.8461</v>
+        <v>-0.7083</v>
       </c>
       <c r="F27" t="n">
-        <v>3.0002</v>
+        <v>-0.0226</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.723</v>
+        <v>-0.7309</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6136</v>
+        <v>-0.8609</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.3366</v>
+        <v>0.1299</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.1608</v>
+        <v>-0.6496</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1111</v>
+        <v>-0.6496</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.2719</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4378</v>
+        <v>-0.0814</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5024</v>
+        <v>-0.2113</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.1299</v>
       </c>
       <c r="P27" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.6418</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0664</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9871</v>
+        <v>-0.0588</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0793</v>
+        <v>0.0588</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2593,25 +2593,25 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>13.4234</v>
+        <v>14.7225</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.4042</v>
+        <v>-3.404200000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>16.8277</v>
+        <v>18.1267</v>
       </c>
       <c r="G28" t="n">
         <v>-3.4067</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8138000000000002</v>
+        <v>0.8138000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>-4.220899999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3117999999999999</v>
+        <v>0.3117999999999997</v>
       </c>
       <c r="K28" t="n">
         <v>1.0718</v>
@@ -2623,31 +2623,31 @@
         <v>-3.7189</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.2583000000000002</v>
+        <v>-0.2583</v>
       </c>
       <c r="O28" t="n">
         <v>-3.4609</v>
       </c>
       <c r="P28" t="n">
-        <v>6.604500000000001</v>
+        <v>6.6045</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.1525</v>
       </c>
       <c r="R28" t="n">
-        <v>20.757</v>
+        <v>20.75700000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>2.830399999999999</v>
+        <v>4.1295</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.3175</v>
+        <v>-1.3174</v>
       </c>
       <c r="U28" t="n">
-        <v>4.1479</v>
+        <v>5.446999999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>7.395200000000001</v>
+        <v>7.395199999999999</v>
       </c>
       <c r="W28" t="n">
         <v>11.7534</v>
